--- a/assessment_forms/019_cupping_knowledge_quiz--assessment_forms.xlsx
+++ b/assessment_forms/019_cupping_knowledge_quiz--assessment_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -437,12 +437,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E28"/>
+  <dimension ref="A1:E18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
-    <col width="31" customWidth="1" min="2" max="2"/>
-    <col width="31" customWidth="1" min="3" max="3"/>
+    <col width="38" customWidth="1" min="2" max="2"/>
+    <col width="50" customWidth="1" min="3" max="3"/>
     <col width="6" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
   </cols>
@@ -520,12 +520,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>first_name</t>
+          <t>cupping_therapy_understanding</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>first_name</t>
+          <t>What is cupping therapy and what does it entail?</t>
         </is>
       </c>
       <c r="D4" t="inlineStr"/>
@@ -538,17 +538,17 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>last_name</t>
+          <t>cupping_therapy_risks</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>last_name</t>
+          <t>Are you aware of the risks associated with cupping therapy?</t>
         </is>
       </c>
       <c r="D5" t="inlineStr"/>
@@ -561,17 +561,17 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_multiple</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>email</t>
+          <t>cupping_therapy_practice</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>email</t>
+          <t>How long have you practiced cupping therapy?</t>
         </is>
       </c>
       <c r="D6" t="inlineStr"/>
@@ -584,17 +584,17 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>phone</t>
+          <t>cupping_therapy_certification</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>phone</t>
+          <t>Have you received any training or certification in cupping therapy?</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
@@ -607,17 +607,17 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_multiple</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>address</t>
+          <t>cupping_therapy_practice_patients</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>address</t>
+          <t>Have you ever practiced cupping therapy on patients?</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
@@ -630,17 +630,17 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>select_one</t>
+          <t>date</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>cupping_therapy_understanding</t>
+          <t>cupping_therapy_certification_date</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>cupping_therapy_understanding</t>
+          <t>What is your certification date for cupping therapy?</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
@@ -653,17 +653,17 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>select_one</t>
+          <t>time</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>cupping_therapy_risks</t>
+          <t>cupping_therapy_certification_time</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>cupping_therapy_risks</t>
+          <t>What is your certification time for cupping therapy?</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
@@ -676,17 +676,17 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>select_multiple</t>
+          <t>note</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>cupping_treatment_procedures</t>
+          <t>note</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>cupping_treatment_procedures</t>
+          <t>Do you have any notes about cupping therapy?</t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
@@ -699,17 +699,17 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>select_one</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>cupping_therapy_certification</t>
+          <t>other_comments</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>cupping_therapy_certification</t>
+          <t>Do you have any other comments about cupping therapy?</t>
         </is>
       </c>
       <c r="D12" t="inlineStr"/>
@@ -722,17 +722,17 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>select_multiple</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>cupping_therapy_practice</t>
+          <t>other_questions</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>cupping_therapy_practice</t>
+          <t>Do you have any other questions about cupping therapy?</t>
         </is>
       </c>
       <c r="D13" t="inlineStr"/>
@@ -745,17 +745,17 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>date</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>date_certification</t>
+          <t>other_notes</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>date_certification</t>
+          <t>Do you have any other notes about cupping therapy?</t>
         </is>
       </c>
       <c r="D14" t="inlineStr"/>
@@ -768,17 +768,17 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>time</t>
+          <t>select_multiple</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>time_certification</t>
+          <t>cupping_therapy_frequency</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>time_certification</t>
+          <t>How often do you practice cupping therapy?</t>
         </is>
       </c>
       <c r="D15" t="inlineStr"/>
@@ -791,17 +791,17 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>note</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>note</t>
+          <t>cupping_therapy_experience</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>note</t>
+          <t>How much experience do you have with cupping therapy?</t>
         </is>
       </c>
       <c r="D16" t="inlineStr"/>
@@ -814,17 +814,17 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>first_name</t>
+          <t>cupping_therapy_certification_level</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>first_name</t>
+          <t>What level of certification do you have in cupping therapy?</t>
         </is>
       </c>
       <c r="D17" t="inlineStr"/>
@@ -837,251 +837,21 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>last_name</t>
+          <t>cupping_therapy_certification_status</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>last_name</t>
+          <t>Are you certified in cupping therapy?</t>
         </is>
       </c>
       <c r="D18" t="inlineStr"/>
       <c r="E18" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>email</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>email</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr"/>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>phone</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>phone</t>
-        </is>
-      </c>
-      <c r="D20" t="inlineStr"/>
-      <c r="E20" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>address</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>address</t>
-        </is>
-      </c>
-      <c r="D21" t="inlineStr"/>
-      <c r="E21" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>select_one</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>cupping_therapy_understanding</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>cupping_therapy_understanding</t>
-        </is>
-      </c>
-      <c r="D22" t="inlineStr"/>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>select_one</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>cupping_therapy_risks</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>cupping_therapy_risks</t>
-        </is>
-      </c>
-      <c r="D23" t="inlineStr"/>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>select_multiple</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>cupping_treatment_procedures</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>cupping_treatment_procedures</t>
-        </is>
-      </c>
-      <c r="D24" t="inlineStr"/>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>select_one</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>cupping_therapy_certification</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>cupping_therapy_certification</t>
-        </is>
-      </c>
-      <c r="D25" t="inlineStr"/>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>select_multiple</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>cupping_therapy_practice</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>cupping_therapy_practice</t>
-        </is>
-      </c>
-      <c r="D26" t="inlineStr"/>
-      <c r="E26" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>date</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>date_certification</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>date_certification</t>
-        </is>
-      </c>
-      <c r="D27" t="inlineStr"/>
-      <c r="E27" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>time</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>time_certification</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>time_certification</t>
-        </is>
-      </c>
-      <c r="D28" t="inlineStr"/>
-      <c r="E28" t="inlineStr">
         <is>
           <t>no</t>
         </is>
@@ -1098,12 +868,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C27"/>
+  <dimension ref="A1:C22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="39" customWidth="1" min="1" max="1"/>
-    <col width="50" customWidth="1" min="2" max="2"/>
-    <col width="50" customWidth="1" min="3" max="3"/>
+    <col width="46" customWidth="1" min="1" max="1"/>
+    <col width="48" customWidth="1" min="2" max="2"/>
+    <col width="48" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1126,442 +896,357 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>cupping_therapy_understanding_choices</t>
+          <t>cupping_therapy_risks_choices</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'label':_'i_understand_what_cupping_therapy_is_and_what_it_entails'}</t>
+          <t>i_am_aware_of_the_risks_of_cupping_therapy</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'label': 'I understand what cupping therapy is and what it entails'}</t>
+          <t>I am aware of the risks of cupping therapy</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>cupping_therapy_understanding_choices</t>
+          <t>cupping_therapy_risks_choices</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'label':_'i_partially_understand_what_cupping_therapy_is'}</t>
+          <t>i_am_not_aware_of_the_risks_of_cupping_therapy</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'label': 'I partially understand what cupping therapy is'}</t>
+          <t>I am not aware of the risks of cupping therapy</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>cupping_therapy_understanding_choices</t>
+          <t>cupping_therapy_practice_choices</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'label':_"i_don't_understand_what_cupping_therapy_is_at_all"}</t>
+          <t>never</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'label': "I don't understand what cupping therapy is at all"}</t>
+          <t>Never</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>cupping_therapy_risks_choices</t>
+          <t>cupping_therapy_practice_choices</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'label':_"i'm_aware_of_the_risks_of_cupping_therapy"}</t>
+          <t>less_than_1_year</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'label': "I'm aware of the risks of cupping therapy"}</t>
+          <t>Less than 1 year</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>cupping_therapy_risks_choices</t>
+          <t>cupping_therapy_practice_choices</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'label':_"i'm_not_aware_of_the_risks_of_cupping_therapy"}</t>
+          <t>1-5_years</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'label': "I'm not aware of the risks of cupping therapy"}</t>
+          <t>1-5 years</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>cupping_treatment_procedures_choices</t>
+          <t>cupping_therapy_practice_choices</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'label':_"i've_received_training_on_cupping_therapy_procedures"}</t>
+          <t>more_than_5_years</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'label': "I've received training on cupping therapy procedures"}</t>
+          <t>More than 5 years</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>cupping_treatment_procedures_choices</t>
+          <t>cupping_therapy_certification_choices</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'label':_"i_haven't_received_training_on_cupping_therapy_procedures"}</t>
+          <t>true</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'label': "I haven't received training on cupping therapy procedures"}</t>
+          <t>True</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>cupping_treatment_procedures_choices</t>
+          <t>cupping_therapy_certification_choices</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'label':_"i'm_not_sure_if_i've_received_training_on_cupping_therapy_procedures"}</t>
+          <t>false</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'label': "I'm not sure if I've received training on cupping therapy procedures"}</t>
+          <t>False</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>cupping_therapy_certification_choices</t>
+          <t>cupping_therapy_practice_patients_choices</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'label':_'i_have_cupping_therapy_certification'}</t>
+          <t>true</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'label': 'I have cupping therapy certification'}</t>
+          <t>True</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>cupping_therapy_certification_choices</t>
+          <t>cupping_therapy_practice_patients_choices</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'label':_"i_don't_have_cupping_therapy_certification"}</t>
+          <t>false</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'label': "I don't have cupping therapy certification"}</t>
+          <t>False</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>cupping_therapy_practice_choices</t>
+          <t>cupping_therapy_frequency_choices</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{'label':_'i_practice_cupping_therapy_with_patients'}</t>
+          <t>daily</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>{'label': 'I practice cupping therapy with patients'}</t>
+          <t>Daily</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>cupping_therapy_practice_choices</t>
+          <t>cupping_therapy_frequency_choices</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>{'label':_'i_practice_cupping_therapy_with_non-patients'}</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>{'label': 'I practice cupping therapy with non-patients'}</t>
+          <t>Weekly</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>cupping_therapy_practice_choices</t>
+          <t>cupping_therapy_frequency_choices</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>{'label':_"i_don't_practice_cupping_therapy"}</t>
+          <t>monthly</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>{'label': "I don't practice cupping therapy"}</t>
+          <t>Monthly</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>cupping_therapy_understanding_choices</t>
+          <t>cupping_therapy_frequency_choices</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>{'label':_'i_understand_what_cupping_therapy_is_and_what_it_entails'}</t>
+          <t>rarely</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>{'label': 'I understand what cupping therapy is and what it entails'}</t>
+          <t>Rarely</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>cupping_therapy_understanding_choices</t>
+          <t>cupping_therapy_experience_choices</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>{'label':_'i_partially_understand_what_cupping_therapy_is'}</t>
+          <t>no_experience</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>{'label': 'I partially understand what cupping therapy is'}</t>
+          <t>No experience</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>cupping_therapy_understanding_choices</t>
+          <t>cupping_therapy_experience_choices</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>{'label':_"i_don't_understand_what_cupping_therapy_is_at_all"}</t>
+          <t>some_experience</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>{'label': "I don't understand what cupping therapy is at all"}</t>
+          <t>Some experience</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>cupping_therapy_risks_choices</t>
+          <t>cupping_therapy_experience_choices</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>{'label':_"i'm_aware_of_the_risks_of_cupping_therapy"}</t>
+          <t>significant_experience</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>{'label': "I'm aware of the risks of cupping therapy"}</t>
+          <t>Significant experience</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>cupping_therapy_risks_choices</t>
+          <t>cupping_therapy_certification_level_choices</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>{'label':_"i'm_not_aware_of_the_risks_of_cupping_therapy"}</t>
+          <t>basic</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>{'label': "I'm not aware of the risks of cupping therapy"}</t>
+          <t>Basic</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>cupping_treatment_procedures_choices</t>
+          <t>cupping_therapy_certification_level_choices</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>{'label':_"i've_received_training_on_cupping_therapy_procedures"}</t>
+          <t>advanced</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>{'label': "I've received training on cupping therapy procedures"}</t>
+          <t>Advanced</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>cupping_treatment_procedures_choices</t>
+          <t>cupping_therapy_certification_status_choices</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>{'label':_"i_haven't_received_training_on_cupping_therapy_procedures"}</t>
+          <t>true</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>{'label': "I haven't received training on cupping therapy procedures"}</t>
+          <t>True</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>cupping_treatment_procedures_choices</t>
+          <t>cupping_therapy_certification_status_choices</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>{'label':_"i'm_not_sure_if_i've_received_training_on_cupping_therapy_procedures"}</t>
+          <t>false</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>{'label': "I'm not sure if I've received training on cupping therapy procedures"}</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>cupping_therapy_certification_choices</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>{'label':_'i_have_cupping_therapy_certification'}</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>{'label': 'I have cupping therapy certification'}</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>cupping_therapy_certification_choices</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>{'label':_"i_don't_have_cupping_therapy_certification"}</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>{'label': "I don't have cupping therapy certification"}</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>cupping_therapy_practice_choices</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>{'label':_'i_practice_cupping_therapy_with_patients'}</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>{'label': 'I practice cupping therapy with patients'}</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>cupping_therapy_practice_choices</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>{'label':_'i_practice_cupping_therapy_with_non-patients'}</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>{'label': 'I practice cupping therapy with non-patients'}</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>cupping_therapy_practice_choices</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>{'label':_"i_don't_practice_cupping_therapy"}</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>{'label': "I don't practice cupping therapy"}</t>
+          <t>False</t>
         </is>
       </c>
     </row>
